--- a/src/media/excel/雨量_注意_新潟デモ更新結果.xlsx
+++ b/src/media/excel/雨量_注意_新潟デモ更新結果.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20250921-002</t>
+          <t>20250921-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/src/media/excel/雨量_注意_新潟デモ更新結果.xlsx
+++ b/src/media/excel/雨量_注意_新潟デモ更新結果.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20250921-001</t>
+          <t>20250921-006</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/src/media/excel/雨量_注意_新潟デモ更新結果.xlsx
+++ b/src/media/excel/雨量_注意_新潟デモ更新結果.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20250921-006</t>
+          <t>20250921-014</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/src/media/excel/雨量_注意_新潟デモ更新結果.xlsx
+++ b/src/media/excel/雨量_注意_新潟デモ更新結果.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20250921-014</t>
+          <t>20250921-017</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/src/media/excel/雨量_注意_新潟デモ更新結果.xlsx
+++ b/src/media/excel/雨量_注意_新潟デモ更新結果.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20250921-017</t>
+          <t>20250921-023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/src/media/excel/雨量_注意_新潟デモ更新結果.xlsx
+++ b/src/media/excel/雨量_注意_新潟デモ更新結果.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20250921-023</t>
+          <t>20250921-026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
